--- a/forms/trg/Formulir_TRG_asds.xlsx
+++ b/forms/trg/Formulir_TRG_asds.xlsx
@@ -564,7 +564,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Formulir kelengkapan data: Applied Statistics and Data Science  Research Group</t>
+          <t>Formulir kelengkapan data: Applied Statistics and Data Science Research Group</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Anggota Applied Statistics and Data Science  Research Group</t>
+          <t>Anggota Applied Statistics and Data Science Research Group</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profil Applied Statistics and Data Science  Research Group</t>
+          <t>Profil Applied Statistics and Data Science Research Group</t>
         </is>
       </c>
     </row>

--- a/forms/trg/Formulir_TRG_asds.xlsx
+++ b/forms/trg/Formulir_TRG_asds.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ID peneliti (SINTA/Scopus/ORCID) banyak yang kosong.</t>
+          <t>Data TRG ini relatif lengkap. Mohon periksa dan lengkapi mitra serta riset terbaik.</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B37)</f>
+        <f>COUNTA(Anggota!B5:B38)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F37)</f>
+        <f>COUNTA(Anggota!F5:F38)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Ainun Mawaddah Abdal, S.Si, M.Si</t>
+          <t>Prof. Sri Astuti Thamrin, S.Si, M.Stat, Ph.D</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -928,16 +928,28 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Risk Management, Actuarial Science</t>
+          <t>Statistical Data Science, Bayesian Methods, Survival Methods, Spatial Analysis, Time Series Analysis</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-2512-0266</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>5975804</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>55980609800</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -950,12 +962,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>A. Muthiah Nur Angriany, S.Si, M.Si</t>
+          <t>Ainun Mawaddah Abdal, S.Si, M.Si</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -965,7 +977,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Risk Management, Actuarial Science</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -987,12 +999,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Eng. Supri Bin Hj Amir, S.Si., M.Eng</t>
+          <t>A. Muthiah Nur Angriany, S.Si, M.Si</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1002,28 +1014,16 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Computer Vision, Machine Learning</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-4185-7003</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
-          <t>6703995</t>
-        </is>
-      </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>57211778159</t>
-        </is>
-      </c>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dian Sidik Arsyad, SKM., MKM., Ph.D</t>
+          <t>Dr. Eng. Supri Bin Hj Amir, S.Si., M.Eng</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1051,16 +1051,28 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Public health, epidemiology, Health Information System, Health Data Science, Biostatistics</t>
+          <t>Computer Vision, Machine Learning</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-4185-7003</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>6703995</t>
+        </is>
+      </c>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>57211778159</t>
+        </is>
+      </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1073,12 +1085,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr Eng. Armin Lawi, S.Si, M.Eng</t>
+          <t>Dian Sidik Arsyad, SKM., MKM., Ph.D</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1088,28 +1100,16 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Computer Science, Distributed Systems , Data Science, Algorithms ,Artificial Intelligence</t>
+          <t>Public health, epidemiology, Health Information System, Health Data Science, Biostatistics</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-1023-6925</t>
-        </is>
-      </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>5976482</t>
-        </is>
-      </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>8651904200</t>
-        </is>
-      </c>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1122,22 +1122,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Kerrie Mengersen</t>
+          <t>Prof. Dr Eng. Armin Lawi, S.Si, M.Eng</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Queensland University of Technology</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>complex systems modelling Bayesian statistical modelling, computational methods and applications Bayesian networks applied statistics.</t>
+          <t>Computer Science, Distributed Systems , Data Science, Algorithms ,Artificial Intelligence</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1146,13 +1146,17 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-8625-9168</t>
-        </is>
-      </c>
-      <c r="K10" s="12" t="n"/>
+          <t>0000-0003-1023-6925</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>5976482</t>
+        </is>
+      </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>6603793565</t>
+          <t>8651904200</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1167,31 +1171,39 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dr. Darfiana Nur</t>
+          <t>Prof. Kerrie Mengersen</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>The University of Western Australia</t>
+          <t>Queensland University of Technology</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Time Series Modelling, Bayesian Inference, Machine Learning / Deep learning</t>
+          <t>complex systems modelling Bayesian statistical modelling, computational methods and applications Bayesian networks applied statistics.</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-8625-9168</t>
+        </is>
+      </c>
       <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>6603793565</t>
+        </is>
+      </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1204,33 +1216,29 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Prof Lu Aye</t>
+          <t>Dr. Darfiana Nur</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>The University of Melbourne, Australia</t>
+          <t>The University of Western Australia</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Complex Systems Modelling &amp; AI</t>
+          <t>Time Series Modelling, Bayesian Inference, Machine Learning / Deep learning</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-5495-1683</t>
-        </is>
-      </c>
+      <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
       <c r="M12" s="11" t="inlineStr">
@@ -1245,25 +1253,33 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Fadil, S.Si.,M.Stat</t>
+          <t>Prof Lu Aye</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="n"/>
+          <t>The University of Melbourne, Australia</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Complex Systems Modelling &amp; AI</t>
+        </is>
+      </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-5495-1683</t>
+        </is>
+      </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n"/>
       <c r="M13" s="11" t="inlineStr">
@@ -1278,24 +1294,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Hedi Kuswanto, S.Si, M.Stat</t>
+          <t>Muhammad Fadil, S.Si.,M.Stat</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Medicine, Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>Data Mining and. Machine Learning</t>
-        </is>
-      </c>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="n"/>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
@@ -1315,22 +1327,22 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Kasim Aidid</t>
+          <t>Hedi Kuswanto, S.Si, M.Stat</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Faculty of Medicine, Hasanuddin University</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>SEM, Spasial dan Komputasi</t>
+          <t>Data Mining and. Machine Learning</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1352,12 +1364,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Rahmawati</t>
+          <t>Muhammad Kasim Aidid</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1365,17 +1377,17 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E16" s="11" t="n"/>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>SEM, Spasial dan Komputasi</t>
+        </is>
+      </c>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="12" t="n"/>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>6454849</t>
-        </is>
-      </c>
+      <c r="K16" s="12" t="n"/>
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="11" t="inlineStr">
         <is>
@@ -1389,12 +1401,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Irna Suryani</t>
+          <t>Rahmawati</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1402,17 +1414,17 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Applied Statistics</t>
-        </is>
-      </c>
+      <c r="E17" s="11" t="n"/>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>6454849</t>
+        </is>
+      </c>
       <c r="L17" s="12" t="n"/>
       <c r="M17" s="11" t="inlineStr">
         <is>
@@ -1426,12 +1438,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Aenun Firdayani</t>
+          <t>Irna Suryani</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1439,7 +1451,11 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E18" s="11" t="n"/>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Applied Statistics</t>
+        </is>
+      </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
@@ -1459,12 +1475,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Nurul Afni Hamzah</t>
+          <t>Aenun Firdayani</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1492,12 +1508,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Angdy Erna</t>
+          <t>Nurul Afni Hamzah</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1505,21 +1521,13 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Data Mining, Operation Research, Deep Multimodal Learning</t>
-        </is>
-      </c>
+      <c r="E20" s="11" t="n"/>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="12" t="n"/>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>6692320</t>
-        </is>
-      </c>
+      <c r="K20" s="12" t="n"/>
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="11" t="inlineStr">
         <is>
@@ -1533,12 +1541,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Imelda Widjaja, S.Si, M.Si</t>
+          <t>Angdy Erna</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1548,7 +1556,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Statistics, Data Science, Education</t>
+          <t>Data Mining, Operation Research, Deep Multimodal Learning</t>
         </is>
       </c>
       <c r="F21" s="12" t="n"/>
@@ -1556,7 +1564,11 @@
       <c r="H21" s="12" t="n"/>
       <c r="I21" s="12" t="n"/>
       <c r="J21" s="12" t="n"/>
-      <c r="K21" s="12" t="n"/>
+      <c r="K21" s="11" t="inlineStr">
+        <is>
+          <t>6692320</t>
+        </is>
+      </c>
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="11" t="inlineStr">
         <is>
@@ -1570,12 +1582,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Dendy Dangkang</t>
+          <t>Imelda Widjaja, S.Si, M.Si</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1585,7 +1597,7 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Statistics, Data Science, Education</t>
         </is>
       </c>
       <c r="F22" s="12" t="n"/>
@@ -1607,12 +1619,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Abd Fatah</t>
+          <t>Dendy Dangkang</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1644,12 +1656,12 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Umi Kalsum</t>
+          <t>Abd Fatah</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -1681,12 +1693,12 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Ahmad Adil Akbar</t>
+          <t>Umi Kalsum</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -1696,7 +1708,7 @@
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F25" s="12" t="n"/>
@@ -1716,10 +1728,26 @@
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="11" t="n"/>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Ahmad Adil Akbar</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Statistics</t>
+        </is>
+      </c>
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="12" t="n"/>
       <c r="H26" s="12" t="n"/>
@@ -1727,7 +1755,11 @@
       <c r="J26" s="12" t="n"/>
       <c r="K26" s="12" t="n"/>
       <c r="L26" s="12" t="n"/>
-      <c r="M26" s="12" t="n"/>
+      <c r="M26" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1916,15 +1948,32 @@
       <c r="L37" s="12" t="n"/>
       <c r="M37" s="12" t="n"/>
     </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="12" t="n"/>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="12" t="n"/>
+      <c r="G38" s="12" t="n"/>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="12" t="n"/>
+      <c r="J38" s="12" t="n"/>
+      <c r="K38" s="12" t="n"/>
+      <c r="L38" s="12" t="n"/>
+      <c r="M38" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
